--- a/光伏配储项目/电价数据/2026/封开站.xlsx
+++ b/光伏配储项目/电价数据/2026/封开站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.50985</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38542</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.7409</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.5709</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.5728</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.49729</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.4925</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.43754</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.45435</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.43889</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.42304</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.41926</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.40875</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.39807</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.39976</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.3849</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.40196</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.42306</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.41253</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.35452</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.39148</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.38492</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.41693</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.39204</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.42063</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.41389</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.42388</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.41284</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.44386</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.3571</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.33702</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.27786</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.29508</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.30671</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.28667</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.30429</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.11209</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.09139</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.09765</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.08265</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.10664</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.04237</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.08391</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>0.09937</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>0.09979</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>0.07948999999999999</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.08942</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>0.06827</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>0.0501</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>0.00224</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.14755</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.21459</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.24005</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.25851</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.20116</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>0.07165000000000001</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>-0.00144</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.26845</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.13048</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.27058</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.26297</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.30095</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.26297</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.17838</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.27644</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.51481</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>0.37075</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.4619</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>0.8158300000000001</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.39212</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>0.5790700000000001</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.42876</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.43971</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.41694</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>0.56379</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.43876</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>0.5882000000000001</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>0.79118</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>0.63405</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>0.6026699999999999</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>0.70916</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>0.77336</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.41548</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.65407</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.6037</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>0.63273</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>0.58051</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.57157</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.63028</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.6000599999999999</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.46462</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.4854</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.40006</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.41597</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.4256</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32935</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.68233</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.61391</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.75824</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.15106</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.8162699999999999</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.5255700000000001</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.51962</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.50545</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.5074</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.49115</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.39992</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.47065</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.37851</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.38025</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.39154</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.33704</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.37056</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.356</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.35907</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.37549</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.37539</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.35944</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.38032</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.41989</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.50257</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.59848</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.67936</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.43105</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.36397</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.40838</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.34762</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.33531</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.4034</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.5004999999999999</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.14632</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.29943</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.35048</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.03622</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.31702</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.33002</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.31062</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.33215</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.32956</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0.34787</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.4683</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.75374</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>0.8746499999999999</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.31657</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.34841</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.3603</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.36266</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.35443</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>0.7346</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>0.47665</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>0.35833</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>0.10122</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.28171</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.30339</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.35788</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.31731</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.3143</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.45843</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.31598</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.25928</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.31352</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.30697</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.24284</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>0.25479</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>0.45113</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>0.41035</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>0.29224</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>0.37379</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>0.34975</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>0.5258400000000001</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>0.64749</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>0.5001100000000001</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>0.68496</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.74851</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>0.75612</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0.49823</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>0.48331</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0.80475</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>0.4829</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0.39532</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>0.87295</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.35403</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.44857</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.59058</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.43961</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.43326</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.41158</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.33568</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.37821</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.3562</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33452</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32149</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.52473</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.36914</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.476</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.3745</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.38161</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.40196</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.39218</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.39013</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.38564</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.36504</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.43321</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.44936</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.33696</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.3708399999999999</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.39602</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.36897</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.37043</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35563</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.36108</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.35138</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.36652</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.3588</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.38432</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.39646</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.47389</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.44927</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.44359</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.34894</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.39773</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.35299</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.36909</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.34852</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.34246</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.30896</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.30205</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.31938</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.19106</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.3420299999999999</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.26559</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.31618</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.31632</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.31744</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.29716</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.34232</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.4624</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.39381</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>0.49789</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.31111</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.46917</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.38274</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>0.29245</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.14235</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.29299</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.24484</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.29374</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.27635</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.27591</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.29342</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.33883</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.30033</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.28192</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.37541</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.37817</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.40224</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.39376</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.4389</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.38809</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.42494</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>0.48938</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.3582</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.37298</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.3344</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.34974</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.49926</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.58646</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>0.4862</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>0.588</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.32676</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.43942</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.40538</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.45296</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.39107</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0.43009</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.42711</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>0.44754</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.43376</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.3807</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.36374</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.40526</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.3862</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.38931</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.39196</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.36034</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.34923</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34257</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.3194</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.37956</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.4006</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.31997</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.36552</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.36044</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.36455</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.34471</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.33734</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.35485</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.33399</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.32939</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.46019</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.33408</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.3285</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.32964</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.33543</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.33512</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.31163</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.31385</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.3107799999999999</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.30756</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.3108399999999999</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.33801</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.33923</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.361</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.38952</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.3366</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.34846</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.32288</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.35132</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.36768</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.36501</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.30555</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.2676</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.29817</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.14107</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.1999</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>0.1506</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.31816</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.25057</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.20783</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.30122</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.50586</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.30303</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.40495</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.3045</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>0.05414</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.05032</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0.11029</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.29406</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.28609</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.14998</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.15929</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.48792</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.05015</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.11669</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.20767</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.23182</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.39009</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.35155</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.31243</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.23021</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.2472</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.21806</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.27567</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>0.14816</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.26953</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.28186</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.30352</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.33571</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.31669</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.33769</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.33858</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.32684</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.36573</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.4174</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.55277</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.45246</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.44354</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.36747</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.35335</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.359</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.36987</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.32514</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.33535</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.32778</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.30757</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.31435</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.32364</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.29477</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.3006</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.31067</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.29718</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.29668</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.29846</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.36975</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.3827</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.35614</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.33903</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.30134</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.31116</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.30905</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.30942</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.30766</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.29415</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.3058999999999999</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.30881</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.29435</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.29873</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.29027</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.29028</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.29035</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.29807</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.29222</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.29521</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.31236</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.3071</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31649</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32448</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32435</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.33275</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32614</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.2795</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.26076</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.04496</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.04667</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.04531</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.04412</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.04838</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.04827</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.04865</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>-0.03546</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>-0.04758</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>-0.04471</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>-0.04193</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>-0.03996</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>-0.04040999999999999</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>-0.04135</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>-0.04093</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>-0.03888</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>-0.04243</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>-0.04586</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>-0.0415</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>-0.04198</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>-0.04306</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>-0.04344</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>-0.04686999999999999</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>-0.04179</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>-0.04543</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.21926</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.04863</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.05438</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.05578</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>-0.00057</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.15128</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.04276</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.10295</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.29003</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.29266</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.29367</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.31993</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.32953</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.3151600000000001</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.33532</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.33445</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.33483</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.33259</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.38498</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.39164</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.38695</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.38583</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.34136</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.40954</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.39959</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.42621</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.46766</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.35457</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.39655</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.40018</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.41744</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.35506</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35811</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34938</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.35523</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.35115</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.36802</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.6681900000000001</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.40043</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.44688</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.42394</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.42403</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.36002</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.35927</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.35827</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.33375</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.30952</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.32481</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.35737</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.3558</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.34778</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.34648</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.33512</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.31562</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.33034</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.3357</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.32284</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.30025</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.32292</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.33543</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.33914</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.35033</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.35212</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.34299</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.3162</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.1025</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.04324</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04679999999999999</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.04568</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04598</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04598</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04598</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04531</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04362</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>-0.03225</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>-0.04217</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.10626</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>-0.00032</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>-0.03846</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>-0.04692</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>-0.04301</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04348</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04348</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.0454</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.04528</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04527</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.04327</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04288</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04512</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04287</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>-0.04114</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.04513</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04494</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.0451</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04315</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04388</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>-0.04056</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>-0.04259</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.04445</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.04996</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.04722999999999999</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.04753</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.20033</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14314</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.29055</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.29527</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.30514</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.30042</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.2955</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.29329</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.29399</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.29298</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.29745</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.2913</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.29545</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.26931</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.29434</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.29854</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.30888</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.3044</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.30239</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.31493</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.31896</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.34815</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.35014</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.34504</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.36704</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.36552</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.33596</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.3309</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.31839</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.31095</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.40519</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.35049</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.32115</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.30782</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31512</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.30185</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.28161</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.2951</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29127</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.28852</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28141</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27162</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27143</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.28149</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.17272</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.15897</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17135</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.14804</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.15978</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15897</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23676</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.21438</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22693</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.26945</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28622</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29122</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.31982</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.29127</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.28141</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.2815</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.28099</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.27068</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28136</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32297</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31075</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.3055</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.31685</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.30974</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.35936</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.31608</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.29331</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.3826</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.38031</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.42705</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.45249</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.33172</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.41699</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.41379</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.38925</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.40122</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.30097</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.2992</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.30005</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15671</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.29242</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.31058</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.31308</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.31161</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.32186</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.3455299999999999</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.30063</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.33086</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.38507</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.50763</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.791</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.62201</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78532</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.49794</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.78099</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.92031</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.4945</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.91727</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.87262</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.30137</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.36314</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.89691</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.6332000000000001</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.19633</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.8733099999999999</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.54996</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.34033</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.03942</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.5403</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.79906</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.5308999999999999</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.7811</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.78398</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.8777699999999999</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.8781100000000001</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.50074</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.40609</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.40969</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.45863</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.21679</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87917</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55123</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.6315499999999999</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.54076</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.50051</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45704</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42543</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.43889</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.45043</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.39065</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45284</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.42039</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.35319</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.40011</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.36535</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.38763</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.41496</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.434</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.34402</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.39055</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.35074</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.3470299999999999</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.3411</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.35025</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.4054700000000001</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.35241</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.45092</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.3551</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.40024</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.40042</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.58739</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.42826</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.5963099999999999</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.60241</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.669</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.46552</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.41666</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.57765</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.45051</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>0.87629</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.63474</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.85366</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>0.8355199999999999</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.86012</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.34241</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.43998</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.33066</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.33167</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.30512</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.31713</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.44393</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.29721</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.28093</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.31018</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.35743</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.33276</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.32059</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.33733</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.33795</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.3179</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.30625</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.31912</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.31982</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.34417</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.31496</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.31513</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.32033</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.30654</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.30303</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.3122200000000001</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.31382</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.31226</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.31559</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.31021</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.31564</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.32265</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.3239</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.32521</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.35476</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.34118</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.34034</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.33844</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.33063</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.33756</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.33558</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.41047</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.41312</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.45298</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.41549</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.39191</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.37537</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.35353</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32876</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.93464</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.36073</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.47068</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.38099</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.44075</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.50007</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.38618</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.41022</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.3744</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.38737</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.36415</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.35039</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.38915</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.33077</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.35943</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.3459100000000001</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.32309</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.40058</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.50081</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.35736</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.38805</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.34372</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.3511</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.35551</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.37095</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.35812</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.36324</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.31662</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.31369</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.33275</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.3383</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.33694</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.34882</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.31509</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.31048</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.29068</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.30491</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.28952</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.28537</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.16494</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.29916</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.30799</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.3239</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.30333</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.31888</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.2972</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.2619</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.19945</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.27732</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.20798</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.31667</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.27726</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.31157</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.31286</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.34456</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.35358</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.31496</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.31135</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.31948</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.30506</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.31294</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.29325</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.30979</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.29051</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.30802</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.31928</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.31329</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.29002</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.34787</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.25561</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.35024</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.32218</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.29379</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.34217</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.27625</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.3499</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.32913</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.34022</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.31016</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.35024</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.32406</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.38585</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.33609</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.43637</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.35023</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.31388</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.42324</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.35147</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.44865</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.32549</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.42081</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.3591</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.40212</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.40086</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.59796</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.35059</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.89042</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.32137</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.12801</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.69369</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.78213</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.64542</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.57729</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.44839</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.44772</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.49659</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.43729</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.43513</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.41295</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.41087</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.42145</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.49721</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.41086</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.43158</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.4114</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.4312</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.38881</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.42606</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.44805</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.3946</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.42121</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.43203</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.41086</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.41083</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.39878</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.42168</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.38312</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.39991</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.49995</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.36225</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.3463</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.29666</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.36539</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.3654</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.30861</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.33971</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.30585</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.3215</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.30382</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.5608300000000001</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.37038</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>0.3172</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.25007</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.54871</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.27609</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.2955</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.28739</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>0.14918</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.39664</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.30256</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.26267</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.25687</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.30507</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.27963</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.28637</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.31143</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.29323</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.3165</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.3102200000000001</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.31974</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.32949</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.31492</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.33976</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.33964</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.39863</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.39863</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.34957</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.35939</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.33995</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.33599</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.37041</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.37066</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.36237</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.37539</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.36304</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.35015</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.57636</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.46108</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>0.7612100000000001</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.46212</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.43786</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.37556</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.42348</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.38634</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.3693</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.33415</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.34082</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.32924</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.32455</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.31865</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.42159</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.33942</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.34394</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.3400899999999999</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.33538</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.32621</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.32947</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.32627</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.32497</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.32431</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.30995</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.3273</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.32595</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.31956</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.31562</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.32024</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.32043</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.30997</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.32455</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.31092</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.3203</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.32068</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.39014</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.32607</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.3495</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.39902</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.37436</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.349</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.33831</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.35403</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.33155</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.33475</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.31873</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.28042</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.3327</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.31672</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.28415</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.30142</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.28721</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.23242</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.14726</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.15139</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.28822</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.15885</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.14631</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.14345</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.14615</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.14398</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.26381</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.14794</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.27277</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.2632</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.1462</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.1221</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.11514</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.10773</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.14097</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.14242</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.14707</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.28314</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.32061</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.32842</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.32233</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.34718</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.3095</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.34606</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.33938</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.36524</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.34155</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.37841</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.34599</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.39671</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.35959</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.38377</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.44786</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.3989</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.39016</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.40073</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.39657</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.44269</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.43787</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.43719</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.44202</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.44177</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.40107</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.38929</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.39652</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.39048</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.35945</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.35982</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.34808</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.34925</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.33952</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.5361</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.38738</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.46549</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.42146</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.41369</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.36926</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.37905</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.37849</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.39129</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.3783</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.36876</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.37906</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.35924</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.38972</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.36923</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.37911</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.34956</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.34664</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.35465</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.34426</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.3397</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.34462</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.3397</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.34426</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.35487</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.36925</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.37903</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.3592</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.33961</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.33986</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.34003</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.32856</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.34228</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.34947</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.36705</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.29454</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.31502</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.31446</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.30691</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.28925</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.28101</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.26606</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.26113</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.19454</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.30357</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.2468</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.23827</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.26533</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.29836</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.28449</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.31512</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.30099</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.29747</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.31176</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.31132</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.2907</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.23797</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.3118</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.30128</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.31037</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.30046</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.28113</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.31626</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.33355</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.33828</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.33146</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.32625</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.32369</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.32491</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.3393</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.35093</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.346</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.35722</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.36614</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.40003</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.39761</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.4011</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.2578</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.36108</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.38079</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.35539</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.35887</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.35492</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.41793</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.35831</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.35462</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.36696</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.37238</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.36012</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.38005</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.38011</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.38489</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.35089</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.35998</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.34018</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.36863</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.43052</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.37052</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.39703</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.38412</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.35254</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.35037</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.36204</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.35153</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.34193</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.34758</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.3456</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.35009</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.35113</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.35012</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.34052</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.34193</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.34289</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.33839</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.33824</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.34355</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.33068</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.3447</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.33263</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.35092</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.3449700000000001</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.36354</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.31394</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.33087</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.33945</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.32629</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.32211</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.33511</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.32411</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>0.29443</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.38706</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.35614</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.30053</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.39757</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.44288</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.32151</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.43219</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.30237</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.29063</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.36742</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>-0.00521</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.2844</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.25055</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.25685</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.08902</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.21419</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.25353</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.29258</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.3156</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.29324</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.27421</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.29932</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.31145</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.3079</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.28993</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.31992</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.34877</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.34574</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.33448</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.4148</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.34069</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.33984</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.34284</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.35247</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.31555</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.38606</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.31881</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.32572</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.32958</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.33476</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.44616</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.44695</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0.71111</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.36311</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0.39043</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.33671</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.32432</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.32574</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.51528</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.2747</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.38615</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.30453</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.32197</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.33216</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.33138</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.30621</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.30998</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.30742</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.29108</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.32543</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.30501</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.3458</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.33582</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.32892</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.32543</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.33068</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.32596</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.32611</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.32025</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.32396</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.32647</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.32436</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.32732</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.32855</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.32711</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.32764</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.32415</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.33144</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.32665</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.32106</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.31994</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.32315</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.32662</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.33118</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.33571</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.35081</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.34118</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.34136</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.33757</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.33904</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.3217</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.32145</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.33443</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.34401</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.34894</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.33469</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.32423</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.32108</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.32059</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.32446</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.31745</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.3408</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.29953</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.35001</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.34427</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.31147</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.32887</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.28362</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.32569</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.31897</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.32186</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.32625</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.32882</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.33442</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.33075</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.32908</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.32673</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.31939</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.32058</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.32042</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.31413</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.35036</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.30892</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.30168</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.3233</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.36003</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.33824</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.34393</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.3341</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.35019</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.35024</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.35026</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.36096</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.33115</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.33065</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.34905</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.38063</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.37278</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.36546</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.3719</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.36654</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.37724</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.36389</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.40038</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.38677</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.37156</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.40482</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.35503</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.38723</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.37925</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.36156</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.35096</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.35015</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.35446</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.34968</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.34256</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.35471</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.3557</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.35252</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.3554</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.35095</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.35015</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.35344</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.35325</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.3498</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.36591</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.35166</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.35548</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.35449</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.33723</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.34329</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.34013</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.34339</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.37679</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.32447</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.34194</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.34329</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.3545</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.34008</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.34345</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.34513</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.33921</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.35447</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.35448</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.33964</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.34005</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.33066</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.35322</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.33906</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.33264</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.33789</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.30344</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.32675</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.32706</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.32825</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.32447</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.31802</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.32856</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.31822</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.31818</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.33052</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.32518</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.32938</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.31805</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.36892</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.32735</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.32065</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.31969</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.31581</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.32625</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.32932</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.32886</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.32207</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.3233</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.33012</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.33062</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.33242</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.33696</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.34493</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.35834</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.40666</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.36545</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.35366</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.35436</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.36575</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.3497</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.35921</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.34598</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.35878</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.35892</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.36091</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.34912</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.38144</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.37964</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.38103</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.38458</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.43769</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.41004</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.39013</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.37906</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.68036</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.78303</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.47461</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.33662</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.45726</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.39224</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.35563</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.35565</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.36562</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.3435299999999999</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.34904</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.32358</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.4163</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.37713</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.37118</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.36238</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.35941</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.35913</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.36228</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.36432</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.36055</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.35925</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.35313</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.36025</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.36057</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.35875</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.35222</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.35954</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.35952</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.35973</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.349</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.37077</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.35883</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.35642</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.36013</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.36013</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.38771</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.3658</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.38175</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.35623</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.35654</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.35074</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.35141</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.36345</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.35424</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.33238</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.32047</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.33512</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.32664</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.2651</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.14638</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.3011</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.28531</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.28399</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.19882</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.25708</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.27984</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.31584</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.27995</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.21828</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.26198</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.28488</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.27815</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.28983</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.29123</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.30515</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.31987</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.32177</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.14996</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.29302</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.2958</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.34871</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.32515</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.34095</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.33567</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.33297</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.34755</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.33126</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.31252</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.33004</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.35845</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.34573</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.35912</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.31665</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.35848</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>0.43332</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>0.38373</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.42344</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.61442</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.6547000000000001</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.6801699999999999</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.48939</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0.7372799999999999</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.52379</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>0.8815499999999999</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.46942</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.48241</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.40794</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.38264</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0.3623</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.4835</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.43068</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.42965</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.38012</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.37484</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.36731</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.36015</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.34399</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.49121</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.55435</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.49842</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.5002799999999999</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.42182</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.40339</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.4078</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.41577</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.40966</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.41912</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.39918</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.39831</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.41434</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.4064700000000001</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.39308</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.38604</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.41623</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.38615</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.41889</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.38848</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.40174</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.4017</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.4142</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.40329</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.44712</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.45566</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.56128</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.49585</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.44729</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.56521</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.46261</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.44177</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.35477</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.38795</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0.38947</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0.42438</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0.42519</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>0.5183</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.4531</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.29736</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.33629</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.36491</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.37864</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.38473</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.4020899999999999</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.32175</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.32898</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.28793</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.3282</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.32189</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.3299</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.34015</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>0.36426</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>0.64048</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0.36488</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0.33623</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.15699</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.28061</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>0.3363</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.32723</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.31165</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.33341</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.34646</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.33069</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.37188</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.35541</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.3701</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.35362</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.3577</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.35277</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.38132</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.33741</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.40996</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.43324</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.48807</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.43525</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.50944</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.53816</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.6051799999999999</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.77535</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>0.7922</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>0.93214</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0.71138</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>0.80338</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.59835</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.55126</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0.9174600000000001</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.84173</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.6293</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.70257</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.45142</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.47143</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.5042099999999999</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.47831</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.49113</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.41835</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.5641499999999999</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.42881</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.4435</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.46757</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.4526</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.43192</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.45553</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.43056</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.40017</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.46846</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.39839</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.40712</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.40781</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.38709</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.3787</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.37375</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.36007</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.35687</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.36585</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.37674</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.37124</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.36019</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.3632</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.36585</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.39449</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.39028</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.38632</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.37094</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.365</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.35767</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.38633</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.4066</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.36966</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.39385</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.39698</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.40338</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.39317</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.35128</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.3691</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.34477</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.33775</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.34602</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.37542</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.18173</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.37917</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.33316</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>0.34719</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.35774</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.34915</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.40542</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.35771</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.44851</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.39093</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.46441</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.32507</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.3132</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>0.11069</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.18103</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.30052</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.29517</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.32036</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.35293</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.34932</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.34874</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.35059</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.37215</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.37841</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.37304</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.38833</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.41573</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.36927</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.42744</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.41232</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.41163</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.38176</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.37534</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.38461</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.39029</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.40895</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.4082</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.34555</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.37223</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.37686</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.40806</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.36007</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.38631</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.35507</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.40154</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.3805</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.37509</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.36361</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.39552</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.38062</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.36562</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.33023</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.44499</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.36053</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.39302</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.39285</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.35647</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.37907</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.35055</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.37876</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.35779</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.35876</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.35551</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.35051</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.35935</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.34648</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.35123</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.34941</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.34023</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.33143</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.34004</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.34036</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.33544</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.34044</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.34545</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.33084</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.33046</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.33182</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.33188</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.33877</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.32003</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.31114</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.30579</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.31862</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.27069</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.32104</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.31583</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.31028</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.22845</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.28872</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.2307</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.28876</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.25048</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.25322</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.13971</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.29252</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.29965</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.31368</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.24996</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.04336</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.25173</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.28759</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.16901</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.18082</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.27264</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.30941</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.30915</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.22774</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.24811</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.26161</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.23171</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.27521</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.28431</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.2825299999999999</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.32642</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.3282</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.30706</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.3529</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.34808</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.35209</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.35931</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.35359</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.35689</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.33122</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.37282</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.35971</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.34437</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.3103</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.35688</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.35795</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.37951</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.35541</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.36906</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.36965</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.36976</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.34527</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.36436</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.37925</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.34145</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.36414</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.36917</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.3605</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.34862</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.34889</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.34861</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.34903</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.3507</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.32191</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.32506</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.33792</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.34152</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.34341</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.33878</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.33036</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.32395</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.31902</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.3183</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.30929</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.30921</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.3141</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.31065</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.30986</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.31098</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.31085</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.31248</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.30684</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.30684</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.30928</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.30661</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.30617</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.30684</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.30733</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.31044</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.31127</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.29098</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.26342</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.25083</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.17178</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.21205</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.20915</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.01782</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.00026</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>-0.02713</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.04975</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.10881</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>-0.01375</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.03974</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.04975</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.02231</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.04466</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.04296</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.049</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.04872</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.02697</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.03273</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.04977</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>0.11684</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.04976</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.04976</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.04964</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>-0.00274</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.28826</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.0498</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.04976</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.03284</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.04975</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.04979</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.04284</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.17095</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.20272</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.24059</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.27951</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.26841</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.27002</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.26917</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.27398</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.28929</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.30883</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.29676</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.29673</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.2836</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.3093</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.306</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.31085</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.29673</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.30871</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.2941</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.30881</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.30074</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.32871</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.40988</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.32778</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.33712</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.31386</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.29632</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.29682</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.28944</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.28872</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.29552</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.15657</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29801</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.59449</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.36225</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.18376</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.34731</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.3022</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.30027</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.27679</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.30854</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.31191</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.29183</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.28284</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.25883</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.24978</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.27502</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.26422</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.2337</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.26122</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.25553</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.28596</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.27839</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.283</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.26113</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.30571</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.28456</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.3194</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.37178</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.31594</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.28503</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.28514</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.23963</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.18095</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>0.6579299999999999</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0.66237</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.6732100000000001</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.5952799999999999</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.17411</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.30926</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.09304999999999999</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>0.24304</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.18762</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.13771</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.14367</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.10203</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.23207</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.12646</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.31683</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>0.05043</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>0.0655</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.11596</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.18465</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>-0.02429</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.1359</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.14084</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.16008</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>-0.01107</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.11932</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.12491</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>0.12625</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.15619</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.25353</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.29229</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.27359</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.3136</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.32693</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.3274</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.32339</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.33461</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.33153</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.33369</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.32837</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.35288</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>0.35827</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>0.37035</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>0.33731</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>0.37914</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>0.37607</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>0.39329</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0.37078</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0.36987</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0.35971</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>0.35964</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.35177</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.36924</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.35254</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.36261</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.37417</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.33288</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.3308</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.32875</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.32975</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.32894</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.34058</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.32386</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.33013</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.3559</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.37163</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.34378</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.33818</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.33803</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.33176</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.33148</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.33157</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.3415899999999999</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.32949</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.34899</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.34087</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.33763</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.3281</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.34994</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.07704000000000001</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.33125</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.32861</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.31905</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.33379</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.32703</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.3409700000000001</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.33252</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.33746</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.34615</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.47897</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.5475599999999999</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.37413</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.41425</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.32345</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.29113</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.31537</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.41134</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.42041</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.35016</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.46018</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.38439</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.45774</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>0.38271</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>0.37274</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.35502</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.43942</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.32564</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.31085</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.32593</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.32854</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.3113</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.13934</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.27405</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.27006</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.30509</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.32689</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.32562</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.32033</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.33197</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.27702</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.30475</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.31106</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.29143</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.31221</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.31796</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.32213</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.32705</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.32854</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.32402</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.34644</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.34402</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.34493</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.34625</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.34597</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.35318</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.33446</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.35731</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.35579</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.33572</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.34965</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.33919</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.36193</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.3766</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.31664</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.44406</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.35771</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.4166</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.35618</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.37527</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.36549</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.35978</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.35531</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.36761</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.35721</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.31089</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.33441</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.32147</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.3332</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.33313</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.37513</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.33145</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.33141</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.28741</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.3166</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.32042</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.33777</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.32928</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.33096</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.33364</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.3424700000000001</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.34512</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.31382</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.35207</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.34021</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.33618</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.32067</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.32053</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.33018</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.34645</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.33118</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.34019</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.35829</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.32325</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.3754</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.35522</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.36943</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.35935</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.35773</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.35064</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.33031</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.35188</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.3828</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.61109</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.32213</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.58569</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0.35342</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.5293099999999999</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.37273</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.36757</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.35332</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.35526</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.30445</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.34606</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.33817</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.39332</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.34959</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.31017</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.33828</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.30768</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.33336</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.26056</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.33283</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.3468</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.34923</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.32778</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.28144</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.28318</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.33456</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.33375</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.3386</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.32439</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.34942</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.36153</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.41465</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.3983</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.50518</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>0.51879</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0.45304</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>0.46457</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.41221</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>0.44441</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.38427</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.40902</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.43073</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.34907</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.39103</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.37368</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.39008</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.38868</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.37382</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.39067</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.4176</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.4633</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.40327</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.38372</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.47995</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.41313</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.38882</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.4131</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.37942</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>1.74342</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.37271</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.51258</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.3749</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.34704</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.47812</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.38375</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.38379</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.36812</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.38075</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.36013</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.37537</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.3742</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.37864</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.37706</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.36903</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.36681</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.36139</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.36005</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.35977</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.3604</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.35554</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.32774</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.35618</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.35038</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.34996</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.34723</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.3501</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.36325</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.37593</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.40914</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.38139</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.36971</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.35884</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.35459</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.34983</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.35848</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.38685</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.40267</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.36938</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.37204</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.43071</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.37694</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.29137</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.35348</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.31729</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.3651</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.26475</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.37755</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.35419</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.35868</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.29378</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.30915</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.32749</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.33383</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.30692</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.32027</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.33995</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.34716</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.31408</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.33334</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.33789</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.33614</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.30428</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.34577</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.3459100000000001</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.38051</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.37242</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.38162</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.36112</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.38809</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.46571</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.39502</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.44476</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.42698</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.42662</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.5112</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.59621</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>0.59389</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>0.39582</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.46276</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>0.57941</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.51202</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.56047</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.52539</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.40778</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>0.56869</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0.52135</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>0.98281</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>0.86863</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.6025900000000001</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.5972499999999999</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.40768</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.46009</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.40889</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.38036</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.37773</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.37298</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.3794</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.27071</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.36973</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.33515</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.36724</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.33897</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.33902</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.34828</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.33043</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.33745</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.34349</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.34078</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.33739</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.36083</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.33906</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.339</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.3415</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.32205</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.33102</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.32464</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.32244</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.32042</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.32332</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.3214</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.31536</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.31861</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.35169</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.37122</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.33218</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.31743</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.31229</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.30762</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.30302</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.34077</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.29701</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.31287</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.31799</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.24441</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.27282</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.28447</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>0.12575</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>0.21249</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.18054</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.05563000000000001</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>0.28674</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.30709</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>0.13304</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>0.02403</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.19422</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0.16278</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>-0.00367</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0.29507</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.25524</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.15386</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.05184</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.04776</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.06115</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.14614</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.06917</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.05233</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.16948</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.13792</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.16345</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.26156</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.29724</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.29962</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.28269</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.36468</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.34734</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.34813</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.36705</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.3493</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.36135</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.26156</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.34926</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.35597</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.34578</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.30953</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.3797</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.39513</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.4085</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.38277</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.41425</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.41899</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.38716</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.39198</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.4241</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.394</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.39107</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.42494</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.38504</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.44536</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.39616</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.38859</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.37256</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.5224800000000001</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.38055</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.34673</v>
+      </c>
+      <c r="C142" t="n">
+        <v>0.9690599999999999</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.36823</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.48242</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.43112</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.38036</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.34751</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.3873</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.37956</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.38478</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.35778</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.3608</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.35302</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.37801</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.35974</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.36488</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.38104</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.38673</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.36204</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.3612</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.36605</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.3646</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.36672</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.36263</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.36852</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.35257</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.38259</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.3470299999999999</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.35249</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.33961</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.31407</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.32485</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.3181</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.33295</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.32668</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.31409</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.29886</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.27577</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.26941</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.28093</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.27068</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.11453</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.01808</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.0182</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.01733</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.03872999999999999</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.17478</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.03986</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>-0.00592</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.01814</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.04557</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.01458</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>0.01321</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.01452</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.16159</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.26183</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.04427</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.24491</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.16049</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.25649</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.30455</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.28795</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.32671</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.30853</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.3137</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.32302</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.31632</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.35828</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.34372</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.48026</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.41646</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.4061</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.36267</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.37122</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.3891</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.36513</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.34408</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.39275</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.55403</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.5781000000000001</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.38647</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.3791600000000001</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.39108</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.39587</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.3726</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.402</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.35489</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.39985</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.42492</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.38538</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.39499</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.36812</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.37389</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.36731</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.36326</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.37545</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.33596</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.5959800000000001</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.3873</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.38928</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.33464</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.37179</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.36546</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.36823</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.35685</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.43885</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.35565</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.39104</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.38009</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.35536</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.35417</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.35969</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.33921</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.3415899999999999</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.35524</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.33942</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.34013</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.34382</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.36164</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.34894</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.35821</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.34977</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.34728</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.35531</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.34195</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.3191000000000001</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.2854100000000001</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.26297</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.23651</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.14737</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.21413</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.23772</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.24135</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.11721</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.15551</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>0.04793</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>0.03612</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.04697</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.04776</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.04658</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.04682</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.04443</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.04179</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.08095000000000001</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.0289</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.06498000000000001</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.0999</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.17658</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>0.20121</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.12403</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.26884</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.23618</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.12709</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.04852</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.26747</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.15167</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.11969</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.24084</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.19257</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.24923</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.25251</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.21047</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.25285</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.2843</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.28584</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.30885</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.31173</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.31512</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.3189</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.34022</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.35168</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.37142</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.34979</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.34042</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.33146</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.35995</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.38759</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.36997</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.37993</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.38692</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.38819</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.40024</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.4128</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.50885</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.40152</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.41092</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.41207</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.40444</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.38226</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.39417</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.409</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.38418</v>
       </c>
     </row>
   </sheetData>
